--- a/nr-prepare-release/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T08:28:57+00:00</t>
+    <t>2026-07-20T08:30:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-cdl-ext-is-emergency.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T08:30:08+00:00</t>
+    <t>2026-07-20T08:39:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
